--- a/PartyCode.xlsx
+++ b/PartyCode.xlsx
@@ -1,42 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\veraj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3241E04D-0CA5-3541-8CDD-C9ADBBCDD9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86241B05-6681-462A-8486-9F0FAF9DC957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
   </bookViews>
   <sheets>
     <sheet name="ORB_PtyUPdateReport" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="536">
   <si>
     <t>Party Code</t>
   </si>
@@ -1644,9 +1633,6 @@
   </si>
   <si>
     <t>ZEPTO LIMITED - West Bengal</t>
-  </si>
-  <si>
-    <t>ZEPTO LIMITED - Coimbatore</t>
   </si>
 </sst>
 </file>
@@ -1753,9 +1739,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1793,7 +1779,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1899,7 +1885,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2041,7 +2027,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2049,17 +2035,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB0927-B5A6-4BE7-9AEA-68E6BA930412}">
-  <dimension ref="A1:E194"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E193"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.24609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.2578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.8125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.2578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2076,7 +2062,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -2093,7 +2079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -2110,7 +2096,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2127,7 +2113,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -2144,7 +2130,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -2161,7 +2147,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -2178,7 +2164,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -2195,7 +2181,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
@@ -2212,7 +2198,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>48</v>
       </c>
@@ -2229,7 +2215,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>51</v>
       </c>
@@ -2246,7 +2232,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
@@ -2263,7 +2249,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>58</v>
       </c>
@@ -2280,7 +2266,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
@@ -2297,7 +2283,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
@@ -2314,7 +2300,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>68</v>
       </c>
@@ -2331,7 +2317,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>71</v>
       </c>
@@ -2348,7 +2334,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>74</v>
       </c>
@@ -2365,7 +2351,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
@@ -2382,7 +2368,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>80</v>
       </c>
@@ -2399,7 +2385,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
@@ -2416,7 +2402,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>86</v>
       </c>
@@ -2433,7 +2419,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>89</v>
       </c>
@@ -2450,7 +2436,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>92</v>
       </c>
@@ -2467,7 +2453,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>95</v>
       </c>
@@ -2484,7 +2470,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>98</v>
       </c>
@@ -2501,7 +2487,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>101</v>
       </c>
@@ -2518,7 +2504,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>104</v>
       </c>
@@ -2535,7 +2521,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>107</v>
       </c>
@@ -2552,7 +2538,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>110</v>
       </c>
@@ -2569,7 +2555,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>113</v>
       </c>
@@ -2586,7 +2572,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>116</v>
       </c>
@@ -2603,7 +2589,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>119</v>
       </c>
@@ -2620,7 +2606,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>122</v>
       </c>
@@ -2637,7 +2623,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>125</v>
       </c>
@@ -2654,7 +2640,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>128</v>
       </c>
@@ -2671,7 +2657,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>131</v>
       </c>
@@ -2688,7 +2674,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>134</v>
       </c>
@@ -2705,7 +2691,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>137</v>
       </c>
@@ -2722,7 +2708,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>140</v>
       </c>
@@ -2739,7 +2725,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>143</v>
       </c>
@@ -2756,7 +2742,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>146</v>
       </c>
@@ -2773,7 +2759,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>149</v>
       </c>
@@ -2790,7 +2776,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>152</v>
       </c>
@@ -2807,7 +2793,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>154</v>
       </c>
@@ -2824,7 +2810,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>156</v>
       </c>
@@ -2841,7 +2827,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>159</v>
       </c>
@@ -2858,7 +2844,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>162</v>
       </c>
@@ -2875,7 +2861,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>165</v>
       </c>
@@ -2892,7 +2878,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>168</v>
       </c>
@@ -2909,7 +2895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>170</v>
       </c>
@@ -2926,7 +2912,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>172</v>
       </c>
@@ -2943,7 +2929,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>176</v>
       </c>
@@ -2960,7 +2946,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>180</v>
       </c>
@@ -2977,7 +2963,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>183</v>
       </c>
@@ -2994,7 +2980,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>186</v>
       </c>
@@ -3011,7 +2997,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>189</v>
       </c>
@@ -3028,7 +3014,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>191</v>
       </c>
@@ -3045,7 +3031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>193</v>
       </c>
@@ -3062,7 +3048,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>195</v>
       </c>
@@ -3079,7 +3065,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>199</v>
       </c>
@@ -3096,7 +3082,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>203</v>
       </c>
@@ -3113,7 +3099,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>206</v>
       </c>
@@ -3130,7 +3116,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>209</v>
       </c>
@@ -3147,7 +3133,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>212</v>
       </c>
@@ -3164,7 +3150,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>214</v>
       </c>
@@ -3181,7 +3167,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>217</v>
       </c>
@@ -3198,7 +3184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>219</v>
       </c>
@@ -3215,7 +3201,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>221</v>
       </c>
@@ -3232,7 +3218,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>225</v>
       </c>
@@ -3249,7 +3235,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>228</v>
       </c>
@@ -3266,7 +3252,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>231</v>
       </c>
@@ -3283,7 +3269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>233</v>
       </c>
@@ -3300,7 +3286,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>237</v>
       </c>
@@ -3317,7 +3303,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>240</v>
       </c>
@@ -3334,7 +3320,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>242</v>
       </c>
@@ -3351,7 +3337,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>245</v>
       </c>
@@ -3368,7 +3354,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>248</v>
       </c>
@@ -3385,7 +3371,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>251</v>
       </c>
@@ -3402,7 +3388,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>253</v>
       </c>
@@ -3419,7 +3405,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>255</v>
       </c>
@@ -3436,7 +3422,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>258</v>
       </c>
@@ -3453,7 +3439,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>261</v>
       </c>
@@ -3470,7 +3456,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>264</v>
       </c>
@@ -3487,7 +3473,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>267</v>
       </c>
@@ -3504,7 +3490,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>270</v>
       </c>
@@ -3521,7 +3507,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>273</v>
       </c>
@@ -3538,7 +3524,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>275</v>
       </c>
@@ -3555,7 +3541,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>277</v>
       </c>
@@ -3572,7 +3558,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>279</v>
       </c>
@@ -3589,7 +3575,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>282</v>
       </c>
@@ -3606,7 +3592,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>288</v>
       </c>
@@ -3623,7 +3609,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>291</v>
       </c>
@@ -3640,7 +3626,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>294</v>
       </c>
@@ -3657,7 +3643,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>297</v>
       </c>
@@ -3674,7 +3660,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>299</v>
       </c>
@@ -3691,7 +3677,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>302</v>
       </c>
@@ -3708,7 +3694,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>305</v>
       </c>
@@ -3725,7 +3711,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>308</v>
       </c>
@@ -3742,7 +3728,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>311</v>
       </c>
@@ -3759,7 +3745,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>313</v>
       </c>
@@ -3776,7 +3762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>315</v>
       </c>
@@ -3793,7 +3779,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>317</v>
       </c>
@@ -3810,7 +3796,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>319</v>
       </c>
@@ -3827,7 +3813,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>322</v>
       </c>
@@ -3844,7 +3830,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>325</v>
       </c>
@@ -3861,7 +3847,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>328</v>
       </c>
@@ -3878,7 +3864,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>331</v>
       </c>
@@ -3895,7 +3881,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>334</v>
       </c>
@@ -3912,7 +3898,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>338</v>
       </c>
@@ -3929,7 +3915,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>341</v>
       </c>
@@ -3946,7 +3932,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>344</v>
       </c>
@@ -3963,7 +3949,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>346</v>
       </c>
@@ -3980,7 +3966,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>348</v>
       </c>
@@ -3997,7 +3983,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>350</v>
       </c>
@@ -4014,7 +4000,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>353</v>
       </c>
@@ -4031,7 +4017,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>356</v>
       </c>
@@ -4048,7 +4034,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>358</v>
       </c>
@@ -4065,7 +4051,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>361</v>
       </c>
@@ -4082,7 +4068,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>363</v>
       </c>
@@ -4099,7 +4085,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>366</v>
       </c>
@@ -4116,7 +4102,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>368</v>
       </c>
@@ -4133,7 +4119,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>371</v>
       </c>
@@ -4150,7 +4136,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>374</v>
       </c>
@@ -4167,7 +4153,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>378</v>
       </c>
@@ -4184,7 +4170,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>381</v>
       </c>
@@ -4201,7 +4187,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>383</v>
       </c>
@@ -4218,7 +4204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>385</v>
       </c>
@@ -4235,7 +4221,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>387</v>
       </c>
@@ -4252,7 +4238,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>389</v>
       </c>
@@ -4269,7 +4255,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>392</v>
       </c>
@@ -4286,7 +4272,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>395</v>
       </c>
@@ -4303,7 +4289,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>397</v>
       </c>
@@ -4320,7 +4306,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>399</v>
       </c>
@@ -4337,7 +4323,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>401</v>
       </c>
@@ -4354,7 +4340,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>403</v>
       </c>
@@ -4371,7 +4357,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>406</v>
       </c>
@@ -4388,7 +4374,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>408</v>
       </c>
@@ -4405,7 +4391,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>411</v>
       </c>
@@ -4422,7 +4408,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>413</v>
       </c>
@@ -4439,7 +4425,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>416</v>
       </c>
@@ -4456,7 +4442,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>418</v>
       </c>
@@ -4473,7 +4459,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>420</v>
       </c>
@@ -4490,7 +4476,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>423</v>
       </c>
@@ -4507,7 +4493,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>426</v>
       </c>
@@ -4524,7 +4510,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>429</v>
       </c>
@@ -4541,7 +4527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>431</v>
       </c>
@@ -4558,7 +4544,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>434</v>
       </c>
@@ -4575,7 +4561,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>436</v>
       </c>
@@ -4592,7 +4578,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>438</v>
       </c>
@@ -4609,7 +4595,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>441</v>
       </c>
@@ -4626,7 +4612,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>443</v>
       </c>
@@ -4643,7 +4629,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>446</v>
       </c>
@@ -4660,7 +4646,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>448</v>
       </c>
@@ -4677,7 +4663,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>450</v>
       </c>
@@ -4694,7 +4680,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>453</v>
       </c>
@@ -4711,7 +4697,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>455</v>
       </c>
@@ -4728,7 +4714,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>458</v>
       </c>
@@ -4745,7 +4731,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>460</v>
       </c>
@@ -4762,7 +4748,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>463</v>
       </c>
@@ -4779,7 +4765,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>465</v>
       </c>
@@ -4796,7 +4782,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>468</v>
       </c>
@@ -4813,7 +4799,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>471</v>
       </c>
@@ -4830,7 +4816,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>473</v>
       </c>
@@ -4847,7 +4833,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>418</v>
       </c>
@@ -4864,7 +4850,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>477</v>
       </c>
@@ -4881,7 +4867,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>480</v>
       </c>
@@ -4898,7 +4884,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>482</v>
       </c>
@@ -4915,7 +4901,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>484</v>
       </c>
@@ -4932,7 +4918,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>486</v>
       </c>
@@ -4949,7 +4935,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>489</v>
       </c>
@@ -4966,7 +4952,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>491</v>
       </c>
@@ -4983,7 +4969,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>494</v>
       </c>
@@ -5000,7 +4986,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>513</v>
       </c>
@@ -5017,7 +5003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>336</v>
       </c>
@@ -5034,7 +5020,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="5">
         <v>5</v>
       </c>
@@ -5051,7 +5037,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>337</v>
       </c>
@@ -5068,7 +5054,7 @@
         <v>122103</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>338</v>
       </c>
@@ -5085,7 +5071,7 @@
         <v>140417</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>340</v>
       </c>
@@ -5102,7 +5088,7 @@
         <v>501510</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>339</v>
       </c>
@@ -5119,7 +5105,7 @@
         <v>501401</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>346</v>
       </c>
@@ -5136,7 +5122,7 @@
         <v>493221</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>341</v>
       </c>
@@ -5153,7 +5139,7 @@
         <v>781122</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>345</v>
       </c>
@@ -5170,7 +5156,7 @@
         <v>711322</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>344</v>
       </c>
@@ -5187,7 +5173,7 @@
         <v>226401</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>342</v>
       </c>
@@ -5204,7 +5190,7 @@
         <v>752054</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>343</v>
       </c>
@@ -5221,7 +5207,7 @@
         <v>804451</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="7">
         <v>347</v>
       </c>
@@ -5238,7 +5224,7 @@
         <v>600067</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="7">
         <v>348</v>
       </c>
@@ -5255,7 +5241,7 @@
         <v>387540</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="7">
         <v>349</v>
       </c>
@@ -5272,7 +5258,7 @@
         <v>209859</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="7">
         <v>350</v>
       </c>
@@ -5289,7 +5275,7 @@
         <v>122506</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="7">
         <v>1003</v>
       </c>
@@ -5306,7 +5292,7 @@
         <v>421302</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="7">
         <v>351</v>
       </c>
@@ -5323,7 +5309,7 @@
         <v>500034</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="7">
         <v>352</v>
       </c>
@@ -5338,23 +5324,6 @@
       </c>
       <c r="E193" s="6">
         <v>712223</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A194" s="7">
-        <v>353</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C194" s="6" t="s">
-        <v>536</v>
-      </c>
-      <c r="D194" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E194" s="6">
-        <v>641402</v>
       </c>
     </row>
   </sheetData>

--- a/PartyCode.xlsx
+++ b/PartyCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\veraj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86241B05-6681-462A-8486-9F0FAF9DC957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA79328-71A2-48EC-8E6C-11858337EF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="536">
   <si>
     <t>Party Code</t>
   </si>
@@ -888,9 +888,6 @@
     <t>500078</t>
   </si>
   <si>
-    <t>711322</t>
-  </si>
-  <si>
     <t>306</t>
   </si>
   <si>
@@ -1284,9 +1281,6 @@
     <t>211</t>
   </si>
   <si>
-    <t>Pathways Retail Private Limited - Kolkata</t>
-  </si>
-  <si>
     <t>198</t>
   </si>
   <si>
@@ -1633,6 +1627,12 @@
   </si>
   <si>
     <t>ZEPTO LIMITED - West Bengal</t>
+  </si>
+  <si>
+    <t>ZEPTO LIMITED - Coimbatore</t>
+  </si>
+  <si>
+    <t>Sliksync Technologies Private Limited -Bangalore</t>
   </si>
 </sst>
 </file>
@@ -2035,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB0927-B5A6-4BE7-9AEA-68E6BA930412}">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E194"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -2053,13 +2053,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2067,7 +2067,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>21</v>
@@ -2084,7 +2084,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>25</v>
@@ -2101,7 +2101,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2118,7 +2118,7 @@
         <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2135,7 +2135,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>36</v>
@@ -2152,7 +2152,7 @@
         <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>40</v>
@@ -2169,7 +2169,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -2186,7 +2186,7 @@
         <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>45</v>
@@ -2203,7 +2203,7 @@
         <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>49</v>
@@ -2220,7 +2220,7 @@
         <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>52</v>
@@ -2237,7 +2237,7 @@
         <v>55</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>56</v>
@@ -2254,7 +2254,7 @@
         <v>58</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>59</v>
@@ -2271,7 +2271,7 @@
         <v>61</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>62</v>
@@ -2288,7 +2288,7 @@
         <v>65</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>66</v>
@@ -2305,7 +2305,7 @@
         <v>68</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>69</v>
@@ -2322,7 +2322,7 @@
         <v>71</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>72</v>
@@ -2339,7 +2339,7 @@
         <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>75</v>
@@ -2356,7 +2356,7 @@
         <v>77</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>78</v>
@@ -2373,7 +2373,7 @@
         <v>80</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>81</v>
@@ -2390,7 +2390,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>84</v>
@@ -2407,7 +2407,7 @@
         <v>86</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>87</v>
@@ -2424,7 +2424,7 @@
         <v>89</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>90</v>
@@ -2441,7 +2441,7 @@
         <v>92</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>93</v>
@@ -2458,7 +2458,7 @@
         <v>95</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>96</v>
@@ -2475,7 +2475,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>99</v>
@@ -2492,7 +2492,7 @@
         <v>101</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>102</v>
@@ -2509,7 +2509,7 @@
         <v>104</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>105</v>
@@ -2526,7 +2526,7 @@
         <v>107</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>108</v>
@@ -2543,7 +2543,7 @@
         <v>110</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>111</v>
@@ -2560,7 +2560,7 @@
         <v>113</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>114</v>
@@ -2577,7 +2577,7 @@
         <v>116</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>117</v>
@@ -2594,7 +2594,7 @@
         <v>119</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>120</v>
@@ -2611,7 +2611,7 @@
         <v>122</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>123</v>
@@ -2628,7 +2628,7 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>126</v>
@@ -2645,7 +2645,7 @@
         <v>128</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>129</v>
@@ -2662,7 +2662,7 @@
         <v>131</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>132</v>
@@ -2679,7 +2679,7 @@
         <v>134</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>135</v>
@@ -2696,7 +2696,7 @@
         <v>137</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>138</v>
@@ -2713,7 +2713,7 @@
         <v>140</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>141</v>
@@ -2730,7 +2730,7 @@
         <v>143</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>144</v>
@@ -2747,7 +2747,7 @@
         <v>146</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>147</v>
@@ -2764,7 +2764,7 @@
         <v>149</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>150</v>
@@ -2781,7 +2781,7 @@
         <v>152</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>153</v>
@@ -2798,7 +2798,7 @@
         <v>154</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>155</v>
@@ -2815,7 +2815,7 @@
         <v>156</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>157</v>
@@ -2832,7 +2832,7 @@
         <v>159</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>160</v>
@@ -2849,7 +2849,7 @@
         <v>162</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>163</v>
@@ -2866,7 +2866,7 @@
         <v>165</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>166</v>
@@ -2883,7 +2883,7 @@
         <v>168</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>169</v>
@@ -2900,7 +2900,7 @@
         <v>170</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>171</v>
@@ -2917,7 +2917,7 @@
         <v>172</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>173</v>
@@ -2934,7 +2934,7 @@
         <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>177</v>
@@ -2951,7 +2951,7 @@
         <v>180</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>181</v>
@@ -2968,7 +2968,7 @@
         <v>183</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>184</v>
@@ -2985,7 +2985,7 @@
         <v>186</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>187</v>
@@ -3002,7 +3002,7 @@
         <v>189</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>190</v>
@@ -3019,7 +3019,7 @@
         <v>191</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>192</v>
@@ -3036,7 +3036,7 @@
         <v>193</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>194</v>
@@ -3053,7 +3053,7 @@
         <v>195</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>196</v>
@@ -3070,7 +3070,7 @@
         <v>199</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>200</v>
@@ -3087,7 +3087,7 @@
         <v>203</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>204</v>
@@ -3104,7 +3104,7 @@
         <v>206</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>207</v>
@@ -3121,7 +3121,7 @@
         <v>209</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>210</v>
@@ -3138,7 +3138,7 @@
         <v>212</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>213</v>
@@ -3155,7 +3155,7 @@
         <v>214</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>215</v>
@@ -3172,7 +3172,7 @@
         <v>217</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>218</v>
@@ -3189,7 +3189,7 @@
         <v>219</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>220</v>
@@ -3206,7 +3206,7 @@
         <v>221</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>222</v>
@@ -3223,7 +3223,7 @@
         <v>225</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>226</v>
@@ -3240,7 +3240,7 @@
         <v>228</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>229</v>
@@ -3257,7 +3257,7 @@
         <v>231</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>232</v>
@@ -3274,7 +3274,7 @@
         <v>233</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>234</v>
@@ -3291,7 +3291,7 @@
         <v>237</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>238</v>
@@ -3308,7 +3308,7 @@
         <v>240</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>241</v>
@@ -3325,7 +3325,7 @@
         <v>242</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>243</v>
@@ -3342,7 +3342,7 @@
         <v>245</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>246</v>
@@ -3359,7 +3359,7 @@
         <v>248</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>249</v>
@@ -3376,7 +3376,7 @@
         <v>251</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>252</v>
@@ -3393,7 +3393,7 @@
         <v>253</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>254</v>
@@ -3410,7 +3410,7 @@
         <v>255</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>256</v>
@@ -3427,7 +3427,7 @@
         <v>258</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>259</v>
@@ -3444,7 +3444,7 @@
         <v>261</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>262</v>
@@ -3461,7 +3461,7 @@
         <v>264</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>265</v>
@@ -3478,7 +3478,7 @@
         <v>267</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>268</v>
@@ -3495,7 +3495,7 @@
         <v>270</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>271</v>
@@ -3512,7 +3512,7 @@
         <v>273</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>274</v>
@@ -3529,7 +3529,7 @@
         <v>275</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>276</v>
@@ -3546,7 +3546,7 @@
         <v>277</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>278</v>
@@ -3563,7 +3563,7 @@
         <v>279</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>280</v>
@@ -3580,7 +3580,7 @@
         <v>282</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>283</v>
@@ -3594,64 +3594,64 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>201</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>22</v>
@@ -3662,81 +3662,81 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>26</v>
@@ -3747,13 +3747,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>5</v>
@@ -3764,13 +3764,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>26</v>
@@ -3781,13 +3781,13 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>37</v>
@@ -3798,149 +3798,149 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>178</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>201</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>37</v>
@@ -3951,13 +3951,13 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>37</v>
@@ -3968,13 +3968,13 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>37</v>
@@ -3985,81 +3985,81 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>357</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>201</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>26</v>
@@ -4070,30 +4070,30 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>37</v>
@@ -4104,81 +4104,81 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C124" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>178</v>
@@ -4189,13 +4189,13 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>7</v>
@@ -4206,13 +4206,13 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>33</v>
@@ -4223,13 +4223,13 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>46</v>
@@ -4240,64 +4240,64 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C130" s="1" t="s">
+      <c r="D130" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>201</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>201</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>5</v>
@@ -4308,13 +4308,13 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>26</v>
@@ -4325,13 +4325,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>402</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>26</v>
@@ -4342,30 +4342,30 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>404</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>223</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>26</v>
@@ -4376,30 +4376,30 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>412</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>26</v>
@@ -4410,36 +4410,36 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -4447,67 +4447,67 @@
         <v>418</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>419</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>287</v>
+        <v>420</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>428</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -4515,7 +4515,7 @@
         <v>429</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>430</v>
@@ -4524,24 +4524,24 @@
         <v>7</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>431</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>433</v>
+        <v>43</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -4549,16 +4549,16 @@
         <v>434</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>435</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -4566,7 +4566,7 @@
         <v>436</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>437</v>
@@ -4575,24 +4575,24 @@
         <v>37</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>185</v>
+        <v>438</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>440</v>
+        <v>43</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -4600,33 +4600,33 @@
         <v>441</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>43</v>
+        <v>443</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>445</v>
+        <v>300</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -4634,16 +4634,16 @@
         <v>446</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>301</v>
+        <v>43</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -4651,33 +4651,33 @@
         <v>448</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>43</v>
+        <v>450</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>452</v>
+        <v>161</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -4685,33 +4685,33 @@
         <v>453</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>454</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>161</v>
+        <v>455</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>457</v>
+        <v>354</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -4719,7 +4719,7 @@
         <v>458</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>459</v>
@@ -4728,24 +4728,24 @@
         <v>7</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>355</v>
+        <v>460</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>462</v>
+        <v>250</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -4753,7 +4753,7 @@
         <v>463</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>464</v>
@@ -4762,41 +4762,41 @@
         <v>33</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>250</v>
+        <v>465</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>470</v>
+        <v>250</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -4804,67 +4804,67 @@
         <v>471</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>472</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>250</v>
+        <v>393</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C164" s="1" t="s">
+      <c r="D164" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>418</v>
+        <v>475</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>479</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -4872,16 +4872,16 @@
         <v>480</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>481</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>433</v>
+        <v>43</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -4889,16 +4889,16 @@
         <v>482</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>483</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -4906,33 +4906,33 @@
         <v>484</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>485</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>185</v>
+        <v>486</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>488</v>
+        <v>43</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -4940,78 +4940,78 @@
         <v>489</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>490</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>43</v>
+        <v>491</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B172" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="D173" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>496</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="4" t="s">
+      <c r="A174" s="5">
+        <v>336</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="D174" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
-        <v>336</v>
+        <v>5</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>515</v>
+        <v>505</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>531</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>26</v>
@@ -5021,309 +5021,326 @@
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="5">
-        <v>5</v>
+      <c r="A176" s="6">
+        <v>337</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>533</v>
+        <v>514</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>43</v>
+        <v>7</v>
+      </c>
+      <c r="E176" s="6">
+        <v>122103</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>7</v>
+        <v>515</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="E177" s="6">
-        <v>122103</v>
+        <v>140417</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E178" s="6">
-        <v>140417</v>
+        <v>501510</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E179" s="6">
-        <v>501510</v>
+        <v>501401</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="C180" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="D180" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="D180" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="E180" s="6">
-        <v>501401</v>
+        <v>493221</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>520</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>521</v>
+        <v>178</v>
       </c>
       <c r="E181" s="6">
-        <v>493221</v>
+        <v>781122</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="E182" s="6">
-        <v>781122</v>
+        <v>711322</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="E183" s="6">
-        <v>711322</v>
+        <v>226401</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
       <c r="E184" s="6">
-        <v>226401</v>
+        <v>752054</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="E185" s="6">
-        <v>752054</v>
+        <v>804451</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="6">
-        <v>343</v>
+      <c r="A186" s="7">
+        <v>347</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>527</v>
+        <v>498</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>526</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="E186" s="6">
-        <v>804451</v>
+        <v>600067</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E187" s="6">
-        <v>600067</v>
+        <v>387540</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E188" s="6">
-        <v>387540</v>
+        <v>209859</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E189" s="6">
-        <v>209859</v>
+        <v>122506</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="7">
-        <v>350</v>
+        <v>1003</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>7</v>
+        <v>530</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="E190" s="6">
-        <v>122506</v>
+        <v>421302</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="7">
-        <v>1003</v>
+        <v>351</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="D191" s="1" t="s">
-        <v>26</v>
+      <c r="D191" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="E191" s="6">
-        <v>421302</v>
+        <v>500034</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c r="E192" s="6">
-        <v>500034</v>
+        <v>712223</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C193" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E193" s="6">
+        <v>641402</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="7">
+        <v>354</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C194" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="D193" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="E193" s="6">
-        <v>712223</v>
+      <c r="D194" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E194" s="6">
+        <v>562107</v>
       </c>
     </row>
   </sheetData>

--- a/PartyCode.xlsx
+++ b/PartyCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\veraj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nidhi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA79328-71A2-48EC-8E6C-11858337EF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06126D5E-B65D-4D80-ACC4-02851701CA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
   </bookViews>
   <sheets>
     <sheet name="ORB_PtyUPdateReport" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="536">
   <si>
     <t>Party Code</t>
   </si>
@@ -1677,7 +1677,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1700,11 +1700,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1720,7 +1731,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1739,9 +1753,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1779,7 +1793,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1885,7 +1899,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2027,7 +2041,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2035,17 +2049,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB0927-B5A6-4BE7-9AEA-68E6BA930412}">
-  <dimension ref="A1:E194"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E195"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2062,7 +2076,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -2079,7 +2093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -2096,7 +2110,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2113,7 +2127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -2130,7 +2144,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -2147,7 +2161,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -2164,7 +2178,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -2181,7 +2195,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
@@ -2198,7 +2212,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>48</v>
       </c>
@@ -2215,7 +2229,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>51</v>
       </c>
@@ -2232,7 +2246,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
@@ -2249,7 +2263,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>58</v>
       </c>
@@ -2266,7 +2280,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
@@ -2283,7 +2297,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
@@ -2300,7 +2314,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>68</v>
       </c>
@@ -2317,7 +2331,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>71</v>
       </c>
@@ -2334,7 +2348,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>74</v>
       </c>
@@ -2351,7 +2365,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
@@ -2368,7 +2382,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>80</v>
       </c>
@@ -2385,7 +2399,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
@@ -2402,7 +2416,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>86</v>
       </c>
@@ -2419,7 +2433,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>89</v>
       </c>
@@ -2436,7 +2450,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>92</v>
       </c>
@@ -2453,7 +2467,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>95</v>
       </c>
@@ -2470,7 +2484,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>98</v>
       </c>
@@ -2487,7 +2501,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>101</v>
       </c>
@@ -2504,7 +2518,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>104</v>
       </c>
@@ -2521,7 +2535,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>107</v>
       </c>
@@ -2538,7 +2552,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>110</v>
       </c>
@@ -2555,7 +2569,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>113</v>
       </c>
@@ -2572,7 +2586,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>116</v>
       </c>
@@ -2589,7 +2603,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>119</v>
       </c>
@@ -2606,7 +2620,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>122</v>
       </c>
@@ -2623,7 +2637,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>125</v>
       </c>
@@ -2640,7 +2654,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>128</v>
       </c>
@@ -2657,7 +2671,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>131</v>
       </c>
@@ -2674,7 +2688,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>134</v>
       </c>
@@ -2691,7 +2705,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>137</v>
       </c>
@@ -2708,7 +2722,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>140</v>
       </c>
@@ -2725,7 +2739,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>143</v>
       </c>
@@ -2742,7 +2756,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>146</v>
       </c>
@@ -2759,7 +2773,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>149</v>
       </c>
@@ -2776,7 +2790,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>152</v>
       </c>
@@ -2793,7 +2807,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>154</v>
       </c>
@@ -2810,7 +2824,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>156</v>
       </c>
@@ -2827,7 +2841,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>159</v>
       </c>
@@ -2844,7 +2858,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>162</v>
       </c>
@@ -2861,7 +2875,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>165</v>
       </c>
@@ -2878,7 +2892,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>168</v>
       </c>
@@ -2895,7 +2909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>170</v>
       </c>
@@ -2912,7 +2926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>172</v>
       </c>
@@ -2929,7 +2943,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>176</v>
       </c>
@@ -2946,7 +2960,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>180</v>
       </c>
@@ -2963,7 +2977,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>183</v>
       </c>
@@ -2980,7 +2994,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>186</v>
       </c>
@@ -2997,7 +3011,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>189</v>
       </c>
@@ -3014,7 +3028,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>191</v>
       </c>
@@ -3031,7 +3045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>193</v>
       </c>
@@ -3048,7 +3062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>195</v>
       </c>
@@ -3065,7 +3079,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>199</v>
       </c>
@@ -3082,7 +3096,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>203</v>
       </c>
@@ -3099,7 +3113,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>206</v>
       </c>
@@ -3116,7 +3130,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>209</v>
       </c>
@@ -3133,7 +3147,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>212</v>
       </c>
@@ -3150,7 +3164,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>214</v>
       </c>
@@ -3167,7 +3181,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>217</v>
       </c>
@@ -3184,7 +3198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>219</v>
       </c>
@@ -3201,7 +3215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>221</v>
       </c>
@@ -3218,7 +3232,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>225</v>
       </c>
@@ -3235,7 +3249,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>228</v>
       </c>
@@ -3252,7 +3266,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>231</v>
       </c>
@@ -3269,7 +3283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>233</v>
       </c>
@@ -3286,7 +3300,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>237</v>
       </c>
@@ -3303,7 +3317,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>240</v>
       </c>
@@ -3320,7 +3334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>242</v>
       </c>
@@ -3337,7 +3351,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>245</v>
       </c>
@@ -3354,7 +3368,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>248</v>
       </c>
@@ -3371,7 +3385,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>251</v>
       </c>
@@ -3388,7 +3402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>253</v>
       </c>
@@ -3405,7 +3419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>255</v>
       </c>
@@ -3422,7 +3436,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>258</v>
       </c>
@@ -3439,7 +3453,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>261</v>
       </c>
@@ -3456,7 +3470,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>264</v>
       </c>
@@ -3473,7 +3487,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>267</v>
       </c>
@@ -3490,7 +3504,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>270</v>
       </c>
@@ -3507,7 +3521,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>273</v>
       </c>
@@ -3524,7 +3538,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>275</v>
       </c>
@@ -3541,7 +3555,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>277</v>
       </c>
@@ -3558,7 +3572,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>279</v>
       </c>
@@ -3575,7 +3589,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>282</v>
       </c>
@@ -3592,7 +3606,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>287</v>
       </c>
@@ -3609,7 +3623,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>290</v>
       </c>
@@ -3626,7 +3640,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>293</v>
       </c>
@@ -3643,7 +3657,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>296</v>
       </c>
@@ -3660,7 +3674,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>298</v>
       </c>
@@ -3677,7 +3691,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>301</v>
       </c>
@@ -3694,7 +3708,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>304</v>
       </c>
@@ -3711,7 +3725,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>307</v>
       </c>
@@ -3728,7 +3742,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>310</v>
       </c>
@@ -3745,7 +3759,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>312</v>
       </c>
@@ -3762,7 +3776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>314</v>
       </c>
@@ -3779,7 +3793,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>316</v>
       </c>
@@ -3796,7 +3810,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>318</v>
       </c>
@@ -3813,7 +3827,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>321</v>
       </c>
@@ -3830,7 +3844,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>324</v>
       </c>
@@ -3847,7 +3861,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>327</v>
       </c>
@@ -3864,7 +3878,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>330</v>
       </c>
@@ -3881,7 +3895,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>333</v>
       </c>
@@ -3898,7 +3912,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>337</v>
       </c>
@@ -3915,7 +3929,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>340</v>
       </c>
@@ -3932,7 +3946,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>343</v>
       </c>
@@ -3949,7 +3963,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>345</v>
       </c>
@@ -3966,7 +3980,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>347</v>
       </c>
@@ -3983,7 +3997,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>349</v>
       </c>
@@ -4000,7 +4014,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>352</v>
       </c>
@@ -4017,7 +4031,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>355</v>
       </c>
@@ -4034,7 +4048,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>357</v>
       </c>
@@ -4051,7 +4065,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>360</v>
       </c>
@@ -4068,7 +4082,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>362</v>
       </c>
@@ -4085,7 +4099,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>365</v>
       </c>
@@ -4102,7 +4116,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>367</v>
       </c>
@@ -4119,7 +4133,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>370</v>
       </c>
@@ -4136,7 +4150,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>373</v>
       </c>
@@ -4153,7 +4167,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>377</v>
       </c>
@@ -4170,7 +4184,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>380</v>
       </c>
@@ -4187,7 +4201,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>382</v>
       </c>
@@ -4204,7 +4218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>384</v>
       </c>
@@ -4221,7 +4235,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>386</v>
       </c>
@@ -4238,7 +4252,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>388</v>
       </c>
@@ -4255,7 +4269,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>391</v>
       </c>
@@ -4272,7 +4286,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>394</v>
       </c>
@@ -4289,7 +4303,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>396</v>
       </c>
@@ -4306,7 +4320,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>398</v>
       </c>
@@ -4323,7 +4337,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>400</v>
       </c>
@@ -4340,7 +4354,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>402</v>
       </c>
@@ -4357,7 +4371,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>405</v>
       </c>
@@ -4374,7 +4388,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>407</v>
       </c>
@@ -4391,7 +4405,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>410</v>
       </c>
@@ -4408,7 +4422,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>412</v>
       </c>
@@ -4425,7 +4439,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>415</v>
       </c>
@@ -4442,7 +4456,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>418</v>
       </c>
@@ -4459,7 +4473,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>421</v>
       </c>
@@ -4476,7 +4490,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>424</v>
       </c>
@@ -4493,7 +4507,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>427</v>
       </c>
@@ -4510,7 +4524,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>429</v>
       </c>
@@ -4527,7 +4541,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>432</v>
       </c>
@@ -4544,7 +4558,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>434</v>
       </c>
@@ -4561,7 +4575,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>436</v>
       </c>
@@ -4578,7 +4592,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>439</v>
       </c>
@@ -4595,7 +4609,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>441</v>
       </c>
@@ -4612,7 +4626,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>444</v>
       </c>
@@ -4629,7 +4643,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>446</v>
       </c>
@@ -4646,7 +4660,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>448</v>
       </c>
@@ -4663,7 +4677,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>451</v>
       </c>
@@ -4680,7 +4694,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>453</v>
       </c>
@@ -4697,7 +4711,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>456</v>
       </c>
@@ -4714,7 +4728,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>458</v>
       </c>
@@ -4731,7 +4745,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>461</v>
       </c>
@@ -4748,7 +4762,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>463</v>
       </c>
@@ -4765,7 +4779,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>466</v>
       </c>
@@ -4782,7 +4796,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>469</v>
       </c>
@@ -4799,7 +4813,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>471</v>
       </c>
@@ -4816,7 +4830,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>417</v>
       </c>
@@ -4833,7 +4847,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>475</v>
       </c>
@@ -4850,7 +4864,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>478</v>
       </c>
@@ -4867,7 +4881,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>480</v>
       </c>
@@ -4884,7 +4898,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>482</v>
       </c>
@@ -4901,7 +4915,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>484</v>
       </c>
@@ -4918,7 +4932,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>487</v>
       </c>
@@ -4935,7 +4949,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>489</v>
       </c>
@@ -4952,7 +4966,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>492</v>
       </c>
@@ -4969,7 +4983,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>511</v>
       </c>
@@ -4986,7 +5000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>336</v>
       </c>
@@ -5003,7 +5017,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>5</v>
       </c>
@@ -5020,7 +5034,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
         <v>337</v>
       </c>
@@ -5037,7 +5051,7 @@
         <v>122103</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
         <v>338</v>
       </c>
@@ -5054,7 +5068,7 @@
         <v>140417</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
         <v>340</v>
       </c>
@@ -5071,7 +5085,7 @@
         <v>501510</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
         <v>339</v>
       </c>
@@ -5088,7 +5102,7 @@
         <v>501401</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
         <v>346</v>
       </c>
@@ -5105,7 +5119,7 @@
         <v>493221</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
         <v>341</v>
       </c>
@@ -5122,7 +5136,7 @@
         <v>781122</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
         <v>345</v>
       </c>
@@ -5139,7 +5153,7 @@
         <v>711322</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
         <v>344</v>
       </c>
@@ -5156,7 +5170,7 @@
         <v>226401</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
         <v>342</v>
       </c>
@@ -5173,7 +5187,7 @@
         <v>752054</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
         <v>343</v>
       </c>
@@ -5190,8 +5204,8 @@
         <v>804451</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="7">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" s="6">
         <v>347</v>
       </c>
       <c r="B186" s="1" t="s">
@@ -5207,8 +5221,8 @@
         <v>600067</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="7">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" s="6">
         <v>348</v>
       </c>
       <c r="B187" s="1" t="s">
@@ -5224,8 +5238,8 @@
         <v>387540</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="7">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" s="6">
         <v>349</v>
       </c>
       <c r="B188" s="1" t="s">
@@ -5241,8 +5255,8 @@
         <v>209859</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="7">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" s="6">
         <v>350</v>
       </c>
       <c r="B189" s="1" t="s">
@@ -5258,8 +5272,8 @@
         <v>122506</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="7">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" s="6">
         <v>1003</v>
       </c>
       <c r="B190" s="1" t="s">
@@ -5275,8 +5289,8 @@
         <v>421302</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="7">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191" s="6">
         <v>351</v>
       </c>
       <c r="B191" s="1" t="s">
@@ -5292,8 +5306,8 @@
         <v>500034</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" s="7">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A192" s="6">
         <v>352</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -5309,8 +5323,8 @@
         <v>712223</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" s="7">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A193" s="6">
         <v>353</v>
       </c>
       <c r="B193" s="1" t="s">
@@ -5326,8 +5340,8 @@
         <v>641402</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A194" s="7">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A194" s="6">
         <v>354</v>
       </c>
       <c r="B194" s="1" t="s">
@@ -5340,6 +5354,23 @@
         <v>37</v>
       </c>
       <c r="E194" s="6">
+        <v>562107</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A195" s="7">
+        <v>111</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E195" s="6">
         <v>562107</v>
       </c>
     </row>

--- a/PartyCode.xlsx
+++ b/PartyCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nidhi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AB724A-8CA6-426B-8B62-EC29B58D516F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF60F71-08E2-493B-ACE0-3E1EFD9A81DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="536">
   <si>
     <t>Party Code</t>
   </si>
@@ -1632,7 +1632,7 @@
     <t>Sliksync Technologies Private Limited -Bangalore</t>
   </si>
   <si>
-    <t>Sliksync</t>
+    <t>Slikk</t>
   </si>
 </sst>
 </file>
@@ -1677,7 +1677,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1700,22 +1700,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1731,10 +1720,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2049,7 +2034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB0927-B5A6-4BE7-9AEA-68E6BA930412}">
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E194"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -5357,23 +5342,6 @@
         <v>562107</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A195" s="7">
-        <v>111</v>
-      </c>
-      <c r="B195" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="C195" s="6" t="s">
-        <v>533</v>
-      </c>
-      <c r="D195" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E195" s="6">
-        <v>562107</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/PartyCode.xlsx
+++ b/PartyCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nidhi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viraj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF60F71-08E2-493B-ACE0-3E1EFD9A81DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919392A1-967D-4A2A-9136-A3E359FBB319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
   </bookViews>
   <sheets>
     <sheet name="ORB_PtyUPdateReport" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="539">
   <si>
     <t>Party Code</t>
   </si>
@@ -1551,6 +1551,9 @@
     <t>Reliance Retail Limited (Tira)</t>
   </si>
   <si>
+    <t xml:space="preserve">Sliksync </t>
+  </si>
+  <si>
     <t>Tata UniStore Limited</t>
   </si>
   <si>
@@ -1632,7 +1635,13 @@
     <t>Sliksync Technologies Private Limited -Bangalore</t>
   </si>
   <si>
-    <t>Slikk</t>
+    <t>CMUNITY INNOVATIONS PRIVATE LIMITED - Haryana</t>
+  </si>
+  <si>
+    <t>City Mall</t>
+  </si>
+  <si>
+    <t>NYKAA E-RETAIL LIMITED -B2B Bengaluru</t>
   </si>
 </sst>
 </file>
@@ -1704,7 +1713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1720,6 +1729,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1738,9 +1751,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1778,7 +1791,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1884,7 +1897,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2026,7 +2039,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2034,17 +2047,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB0927-B5A6-4BE7-9AEA-68E6BA930412}">
-  <dimension ref="A1:E194"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E196"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2061,7 +2074,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -2078,7 +2091,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -2095,7 +2108,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2112,7 +2125,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -2129,7 +2142,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -2146,7 +2159,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -2163,7 +2176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -2180,7 +2193,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
@@ -2197,7 +2210,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>48</v>
       </c>
@@ -2214,7 +2227,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>51</v>
       </c>
@@ -2231,7 +2244,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
@@ -2248,7 +2261,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>58</v>
       </c>
@@ -2265,7 +2278,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
@@ -2282,7 +2295,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
@@ -2299,7 +2312,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>68</v>
       </c>
@@ -2316,7 +2329,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>71</v>
       </c>
@@ -2333,7 +2346,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>74</v>
       </c>
@@ -2350,7 +2363,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
@@ -2367,7 +2380,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>80</v>
       </c>
@@ -2384,7 +2397,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
@@ -2401,7 +2414,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>86</v>
       </c>
@@ -2418,7 +2431,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>89</v>
       </c>
@@ -2435,7 +2448,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>92</v>
       </c>
@@ -2452,7 +2465,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>95</v>
       </c>
@@ -2469,7 +2482,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>98</v>
       </c>
@@ -2486,7 +2499,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>101</v>
       </c>
@@ -2503,7 +2516,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>104</v>
       </c>
@@ -2520,7 +2533,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>107</v>
       </c>
@@ -2537,7 +2550,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>110</v>
       </c>
@@ -2554,7 +2567,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>113</v>
       </c>
@@ -2571,7 +2584,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>116</v>
       </c>
@@ -2588,7 +2601,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>119</v>
       </c>
@@ -2605,7 +2618,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>122</v>
       </c>
@@ -2622,7 +2635,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>125</v>
       </c>
@@ -2639,7 +2652,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>128</v>
       </c>
@@ -2656,7 +2669,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>131</v>
       </c>
@@ -2673,7 +2686,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>134</v>
       </c>
@@ -2690,7 +2703,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>137</v>
       </c>
@@ -2707,7 +2720,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>140</v>
       </c>
@@ -2724,7 +2737,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>143</v>
       </c>
@@ -2741,7 +2754,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>146</v>
       </c>
@@ -2758,7 +2771,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>149</v>
       </c>
@@ -2775,7 +2788,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>152</v>
       </c>
@@ -2792,7 +2805,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>154</v>
       </c>
@@ -2809,7 +2822,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>156</v>
       </c>
@@ -2826,7 +2839,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>159</v>
       </c>
@@ -2843,7 +2856,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>162</v>
       </c>
@@ -2860,7 +2873,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>165</v>
       </c>
@@ -2877,7 +2890,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>168</v>
       </c>
@@ -2894,7 +2907,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>170</v>
       </c>
@@ -2911,7 +2924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>172</v>
       </c>
@@ -2928,7 +2941,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>176</v>
       </c>
@@ -2945,7 +2958,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>180</v>
       </c>
@@ -2962,7 +2975,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>183</v>
       </c>
@@ -2979,7 +2992,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>186</v>
       </c>
@@ -2996,7 +3009,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>189</v>
       </c>
@@ -3013,7 +3026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>191</v>
       </c>
@@ -3030,7 +3043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>193</v>
       </c>
@@ -3047,7 +3060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>195</v>
       </c>
@@ -3064,7 +3077,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>199</v>
       </c>
@@ -3081,7 +3094,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>203</v>
       </c>
@@ -3098,7 +3111,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>206</v>
       </c>
@@ -3115,7 +3128,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>209</v>
       </c>
@@ -3132,7 +3145,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>212</v>
       </c>
@@ -3149,7 +3162,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>214</v>
       </c>
@@ -3166,7 +3179,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>217</v>
       </c>
@@ -3183,7 +3196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>219</v>
       </c>
@@ -3200,7 +3213,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>221</v>
       </c>
@@ -3217,7 +3230,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>225</v>
       </c>
@@ -3234,7 +3247,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>228</v>
       </c>
@@ -3251,7 +3264,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>231</v>
       </c>
@@ -3268,7 +3281,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>233</v>
       </c>
@@ -3285,7 +3298,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>237</v>
       </c>
@@ -3302,7 +3315,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>240</v>
       </c>
@@ -3319,7 +3332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>242</v>
       </c>
@@ -3336,7 +3349,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>245</v>
       </c>
@@ -3353,7 +3366,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>248</v>
       </c>
@@ -3370,7 +3383,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>251</v>
       </c>
@@ -3387,7 +3400,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>253</v>
       </c>
@@ -3404,7 +3417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>255</v>
       </c>
@@ -3421,7 +3434,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>258</v>
       </c>
@@ -3438,7 +3451,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>261</v>
       </c>
@@ -3455,7 +3468,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>264</v>
       </c>
@@ -3472,7 +3485,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>267</v>
       </c>
@@ -3489,7 +3502,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>270</v>
       </c>
@@ -3506,7 +3519,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>273</v>
       </c>
@@ -3523,7 +3536,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>275</v>
       </c>
@@ -3540,7 +3553,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>277</v>
       </c>
@@ -3557,7 +3570,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>279</v>
       </c>
@@ -3574,7 +3587,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>282</v>
       </c>
@@ -3591,7 +3604,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>287</v>
       </c>
@@ -3608,7 +3621,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>290</v>
       </c>
@@ -3625,7 +3638,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>293</v>
       </c>
@@ -3642,7 +3655,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>296</v>
       </c>
@@ -3659,7 +3672,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>298</v>
       </c>
@@ -3676,7 +3689,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>301</v>
       </c>
@@ -3693,7 +3706,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>304</v>
       </c>
@@ -3710,7 +3723,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>307</v>
       </c>
@@ -3727,7 +3740,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>310</v>
       </c>
@@ -3744,7 +3757,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>312</v>
       </c>
@@ -3761,7 +3774,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>314</v>
       </c>
@@ -3778,7 +3791,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>316</v>
       </c>
@@ -3795,7 +3808,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>318</v>
       </c>
@@ -3812,7 +3825,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>321</v>
       </c>
@@ -3829,7 +3842,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>324</v>
       </c>
@@ -3846,7 +3859,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>327</v>
       </c>
@@ -3863,7 +3876,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>330</v>
       </c>
@@ -3880,7 +3893,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>333</v>
       </c>
@@ -3897,7 +3910,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>337</v>
       </c>
@@ -3914,7 +3927,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>340</v>
       </c>
@@ -3931,7 +3944,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>343</v>
       </c>
@@ -3948,7 +3961,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>345</v>
       </c>
@@ -3965,7 +3978,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>347</v>
       </c>
@@ -3982,7 +3995,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>349</v>
       </c>
@@ -3999,7 +4012,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>352</v>
       </c>
@@ -4016,7 +4029,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>355</v>
       </c>
@@ -4033,7 +4046,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>357</v>
       </c>
@@ -4050,7 +4063,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>360</v>
       </c>
@@ -4067,7 +4080,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>362</v>
       </c>
@@ -4084,7 +4097,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>365</v>
       </c>
@@ -4101,7 +4114,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>367</v>
       </c>
@@ -4118,7 +4131,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>370</v>
       </c>
@@ -4135,7 +4148,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>373</v>
       </c>
@@ -4152,7 +4165,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>377</v>
       </c>
@@ -4169,7 +4182,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>380</v>
       </c>
@@ -4186,7 +4199,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>382</v>
       </c>
@@ -4203,7 +4216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>384</v>
       </c>
@@ -4220,7 +4233,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>386</v>
       </c>
@@ -4237,7 +4250,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>388</v>
       </c>
@@ -4254,7 +4267,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>391</v>
       </c>
@@ -4271,7 +4284,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>394</v>
       </c>
@@ -4288,7 +4301,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>396</v>
       </c>
@@ -4305,7 +4318,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>398</v>
       </c>
@@ -4322,7 +4335,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>400</v>
       </c>
@@ -4339,7 +4352,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>402</v>
       </c>
@@ -4356,7 +4369,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>405</v>
       </c>
@@ -4373,7 +4386,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>407</v>
       </c>
@@ -4390,7 +4403,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>410</v>
       </c>
@@ -4407,7 +4420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>412</v>
       </c>
@@ -4424,7 +4437,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>415</v>
       </c>
@@ -4441,7 +4454,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>418</v>
       </c>
@@ -4458,7 +4471,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>421</v>
       </c>
@@ -4475,7 +4488,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>424</v>
       </c>
@@ -4492,7 +4505,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>427</v>
       </c>
@@ -4509,7 +4522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>429</v>
       </c>
@@ -4526,7 +4539,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>432</v>
       </c>
@@ -4543,7 +4556,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>434</v>
       </c>
@@ -4560,12 +4573,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>436</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>535</v>
+        <v>508</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>437</v>
@@ -4577,12 +4590,12 @@
         <v>438</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>439</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>440</v>
@@ -4594,12 +4607,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>441</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>442</v>
@@ -4611,12 +4624,12 @@
         <v>443</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>444</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>445</v>
@@ -4628,12 +4641,12 @@
         <v>300</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>446</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>447</v>
@@ -4645,12 +4658,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>448</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>449</v>
@@ -4662,12 +4675,12 @@
         <v>450</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>451</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>452</v>
@@ -4679,12 +4692,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>453</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>454</v>
@@ -4696,12 +4709,12 @@
         <v>455</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>456</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>457</v>
@@ -4713,12 +4726,12 @@
         <v>354</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>458</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>459</v>
@@ -4730,12 +4743,12 @@
         <v>460</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>461</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>462</v>
@@ -4747,12 +4760,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>464</v>
@@ -4764,12 +4777,12 @@
         <v>465</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>466</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>467</v>
@@ -4781,12 +4794,12 @@
         <v>468</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>469</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>470</v>
@@ -4798,12 +4811,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>471</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>472</v>
@@ -4815,12 +4828,12 @@
         <v>393</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>417</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>473</v>
@@ -4832,12 +4845,12 @@
         <v>474</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>475</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>476</v>
@@ -4849,12 +4862,12 @@
         <v>477</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>478</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>479</v>
@@ -4866,12 +4879,12 @@
         <v>431</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>480</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>481</v>
@@ -4883,12 +4896,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>482</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>483</v>
@@ -4900,12 +4913,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>484</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>485</v>
@@ -4917,12 +4930,12 @@
         <v>486</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>487</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>488</v>
@@ -4934,12 +4947,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>489</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>490</v>
@@ -4951,12 +4964,12 @@
         <v>491</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>492</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>493</v>
@@ -4968,15 +4981,15 @@
         <v>494</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>505</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>7</v>
@@ -4985,7 +4998,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>336</v>
       </c>
@@ -4993,7 +5006,7 @@
         <v>505</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>26</v>
@@ -5002,7 +5015,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>5</v>
       </c>
@@ -5010,7 +5023,7 @@
         <v>505</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>26</v>
@@ -5019,15 +5032,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>337</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>7</v>
@@ -5036,15 +5049,15 @@
         <v>122103</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>338</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D177" s="6" t="s">
         <v>13</v>
@@ -5053,7 +5066,7 @@
         <v>140417</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>340</v>
       </c>
@@ -5061,7 +5074,7 @@
         <v>498</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D178" s="6" t="s">
         <v>33</v>
@@ -5070,15 +5083,15 @@
         <v>501510</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>339</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>33</v>
@@ -5087,7 +5100,7 @@
         <v>501401</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>346</v>
       </c>
@@ -5095,24 +5108,24 @@
         <v>498</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E180" s="6">
         <v>493221</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>341</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D181" s="6" t="s">
         <v>178</v>
@@ -5121,15 +5134,15 @@
         <v>781122</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>345</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>201</v>
@@ -5138,15 +5151,15 @@
         <v>711322</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>344</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D183" s="6" t="s">
         <v>5</v>
@@ -5155,15 +5168,15 @@
         <v>226401</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>342</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>197</v>
@@ -5172,15 +5185,15 @@
         <v>752054</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>343</v>
       </c>
       <c r="B185" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C185" s="6" t="s">
         <v>524</v>
-      </c>
-      <c r="C185" s="6" t="s">
-        <v>523</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>223</v>
@@ -5189,15 +5202,15 @@
         <v>804451</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" s="6">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="7">
         <v>347</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>498</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>53</v>
@@ -5206,15 +5219,15 @@
         <v>600067</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" s="6">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="7">
         <v>348</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>498</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>22</v>
@@ -5223,15 +5236,15 @@
         <v>387540</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="6">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="7">
         <v>349</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>498</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>5</v>
@@ -5240,15 +5253,15 @@
         <v>209859</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="6">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="7">
         <v>350</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>505</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>7</v>
@@ -5257,15 +5270,15 @@
         <v>122506</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" s="6">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="7">
         <v>1003</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>505</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>26</v>
@@ -5274,15 +5287,15 @@
         <v>421302</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191" s="6">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="7">
         <v>351</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>501</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D191" s="6" t="s">
         <v>33</v>
@@ -5291,15 +5304,15 @@
         <v>500034</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A192" s="6">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="7">
         <v>352</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D192" s="6" t="s">
         <v>201</v>
@@ -5308,15 +5321,15 @@
         <v>712223</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A193" s="6">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="7">
         <v>353</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D193" s="6" t="s">
         <v>53</v>
@@ -5325,21 +5338,55 @@
         <v>641402</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A194" s="6">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="7">
         <v>354</v>
       </c>
       <c r="B194" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C194" s="6" t="s">
         <v>535</v>
-      </c>
-      <c r="C194" s="6" t="s">
-        <v>534</v>
       </c>
       <c r="D194" s="6" t="s">
         <v>37</v>
       </c>
       <c r="E194" s="6">
         <v>562107</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="7">
+        <v>355</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E195" s="6">
+        <v>131101</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="7">
+        <v>356</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E196" s="6">
+        <v>562114</v>
       </c>
     </row>
   </sheetData>

--- a/PartyCode.xlsx
+++ b/PartyCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viraj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919392A1-967D-4A2A-9136-A3E359FBB319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA291DA-667E-4139-8DB1-E3E002A1F4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="540">
   <si>
     <t>Party Code</t>
   </si>
@@ -1642,6 +1642,9 @@
   </si>
   <si>
     <t>NYKAA E-RETAIL LIMITED -B2B Bengaluru</t>
+  </si>
+  <si>
+    <t>Reliance Retail Limited-NELAMANGALA</t>
   </si>
 </sst>
 </file>
@@ -2047,7 +2050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB0927-B5A6-4BE7-9AEA-68E6BA930412}">
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -5389,6 +5392,23 @@
         <v>562114</v>
       </c>
     </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="7">
+        <v>357</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E197" s="6">
+        <v>562123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/PartyCode.xlsx
+++ b/PartyCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viraj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA291DA-667E-4139-8DB1-E3E002A1F4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919392A1-967D-4A2A-9136-A3E359FBB319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="539">
   <si>
     <t>Party Code</t>
   </si>
@@ -1642,9 +1642,6 @@
   </si>
   <si>
     <t>NYKAA E-RETAIL LIMITED -B2B Bengaluru</t>
-  </si>
-  <si>
-    <t>Reliance Retail Limited-NELAMANGALA</t>
   </si>
 </sst>
 </file>
@@ -2050,7 +2047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB0927-B5A6-4BE7-9AEA-68E6BA930412}">
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -5392,23 +5389,6 @@
         <v>562114</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A197" s="7">
-        <v>357</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C197" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="D197" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E197" s="6">
-        <v>562123</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/PartyCode.xlsx
+++ b/PartyCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viraj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919392A1-967D-4A2A-9136-A3E359FBB319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0696F7-C91C-4E16-B372-CAB47D552F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="540">
   <si>
     <t>Party Code</t>
   </si>
@@ -1642,6 +1642,9 @@
   </si>
   <si>
     <t>NYKAA E-RETAIL LIMITED -B2B Bengaluru</t>
+  </si>
+  <si>
+    <t>Reliance Retail Limited-NELAMANGALA</t>
   </si>
 </sst>
 </file>
@@ -2047,7 +2050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB0927-B5A6-4BE7-9AEA-68E6BA930412}">
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -5389,6 +5392,23 @@
         <v>562114</v>
       </c>
     </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="7">
+        <v>357</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E197" s="6">
+        <v>562123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/PartyCode.xlsx
+++ b/PartyCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viraj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0696F7-C91C-4E16-B372-CAB47D552F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305FD5B0-E07C-4892-A6DF-4A29D3CA32A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{99EBD75F-AF2A-43B3-9555-8F8B52E04ADC}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="541">
   <si>
     <t>Party Code</t>
   </si>
@@ -1257,27 +1257,6 @@
     <t>140401</t>
   </si>
   <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>Pathways Retail Private Limited -BHIWANDI</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>Pathways Retail Private Limited - HARYANA</t>
-  </si>
-  <si>
-    <t>122503</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>Pathways Retail Private Limited - KARNATAKA</t>
-  </si>
-  <si>
     <t>211</t>
   </si>
   <si>
@@ -1645,6 +1624,30 @@
   </si>
   <si>
     <t>Reliance Retail Limited-NELAMANGALA</t>
+  </si>
+  <si>
+    <t>Flipkart India Pvt. Ltd - Bangalore</t>
+  </si>
+  <si>
+    <t>Flipkart India Private Limited - Haryana</t>
+  </si>
+  <si>
+    <t>Flipkart India Private Limited -Bengaluru</t>
+  </si>
+  <si>
+    <t>Flipkart India Private Limited -Bhiwandi</t>
+  </si>
+  <si>
+    <t>Flipkart India Private Limited -Gurgaon</t>
+  </si>
+  <si>
+    <t>Flipkart India Private Limited -West Bengal</t>
+  </si>
+  <si>
+    <t>Flipkart India Private Limited - Sonipat</t>
+  </si>
+  <si>
+    <t>Flipkart India Private Limited -Howrah</t>
   </si>
 </sst>
 </file>
@@ -2050,7 +2053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB0927-B5A6-4BE7-9AEA-68E6BA930412}">
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E202"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -2068,13 +2071,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2082,7 +2085,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>21</v>
@@ -2099,7 +2102,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>25</v>
@@ -2116,7 +2119,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2133,7 +2136,7 @@
         <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2150,7 +2153,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>36</v>
@@ -2167,7 +2170,7 @@
         <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>40</v>
@@ -2184,7 +2187,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -2201,7 +2204,7 @@
         <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>45</v>
@@ -2218,7 +2221,7 @@
         <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>49</v>
@@ -2235,7 +2238,7 @@
         <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>52</v>
@@ -2252,7 +2255,7 @@
         <v>55</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>56</v>
@@ -2269,7 +2272,7 @@
         <v>58</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>59</v>
@@ -2286,7 +2289,7 @@
         <v>61</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>62</v>
@@ -2303,7 +2306,7 @@
         <v>65</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>66</v>
@@ -2320,7 +2323,7 @@
         <v>68</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>69</v>
@@ -2337,7 +2340,7 @@
         <v>71</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>72</v>
@@ -2354,7 +2357,7 @@
         <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>75</v>
@@ -2371,7 +2374,7 @@
         <v>77</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>78</v>
@@ -2388,7 +2391,7 @@
         <v>80</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>81</v>
@@ -2405,7 +2408,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>84</v>
@@ -2422,7 +2425,7 @@
         <v>86</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>87</v>
@@ -2439,7 +2442,7 @@
         <v>89</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>90</v>
@@ -2456,7 +2459,7 @@
         <v>92</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>93</v>
@@ -2473,7 +2476,7 @@
         <v>95</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>96</v>
@@ -2490,7 +2493,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>99</v>
@@ -2507,7 +2510,7 @@
         <v>101</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>102</v>
@@ -2524,7 +2527,7 @@
         <v>104</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>105</v>
@@ -2541,7 +2544,7 @@
         <v>107</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>108</v>
@@ -2558,7 +2561,7 @@
         <v>110</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>111</v>
@@ -2575,7 +2578,7 @@
         <v>113</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>114</v>
@@ -2592,7 +2595,7 @@
         <v>116</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>117</v>
@@ -2609,7 +2612,7 @@
         <v>119</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>120</v>
@@ -2626,7 +2629,7 @@
         <v>122</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>123</v>
@@ -2643,7 +2646,7 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>126</v>
@@ -2660,7 +2663,7 @@
         <v>128</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>129</v>
@@ -2677,7 +2680,7 @@
         <v>131</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>132</v>
@@ -2694,7 +2697,7 @@
         <v>134</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>135</v>
@@ -2711,7 +2714,7 @@
         <v>137</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>138</v>
@@ -2728,7 +2731,7 @@
         <v>140</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>141</v>
@@ -2745,7 +2748,7 @@
         <v>143</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>144</v>
@@ -2762,7 +2765,7 @@
         <v>146</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>147</v>
@@ -2779,7 +2782,7 @@
         <v>149</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>150</v>
@@ -2796,7 +2799,7 @@
         <v>152</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>153</v>
@@ -2813,7 +2816,7 @@
         <v>154</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>155</v>
@@ -2830,7 +2833,7 @@
         <v>156</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>157</v>
@@ -2847,7 +2850,7 @@
         <v>159</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>160</v>
@@ -2864,7 +2867,7 @@
         <v>162</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>163</v>
@@ -2881,7 +2884,7 @@
         <v>165</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>166</v>
@@ -2898,7 +2901,7 @@
         <v>168</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>169</v>
@@ -2915,7 +2918,7 @@
         <v>170</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>171</v>
@@ -2932,7 +2935,7 @@
         <v>172</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>173</v>
@@ -2949,7 +2952,7 @@
         <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>177</v>
@@ -2966,7 +2969,7 @@
         <v>180</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>181</v>
@@ -2983,7 +2986,7 @@
         <v>183</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>184</v>
@@ -3000,7 +3003,7 @@
         <v>186</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>187</v>
@@ -3017,7 +3020,7 @@
         <v>189</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>190</v>
@@ -3034,7 +3037,7 @@
         <v>191</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>192</v>
@@ -3051,7 +3054,7 @@
         <v>193</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>194</v>
@@ -3068,7 +3071,7 @@
         <v>195</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>196</v>
@@ -3085,7 +3088,7 @@
         <v>199</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>200</v>
@@ -3102,7 +3105,7 @@
         <v>203</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>204</v>
@@ -3119,7 +3122,7 @@
         <v>206</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>207</v>
@@ -3136,7 +3139,7 @@
         <v>209</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>210</v>
@@ -3153,7 +3156,7 @@
         <v>212</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>213</v>
@@ -3170,7 +3173,7 @@
         <v>214</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>215</v>
@@ -3187,7 +3190,7 @@
         <v>217</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>218</v>
@@ -3204,7 +3207,7 @@
         <v>219</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>220</v>
@@ -3221,7 +3224,7 @@
         <v>221</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>222</v>
@@ -3238,7 +3241,7 @@
         <v>225</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>226</v>
@@ -3255,7 +3258,7 @@
         <v>228</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>229</v>
@@ -3272,7 +3275,7 @@
         <v>231</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>232</v>
@@ -3289,7 +3292,7 @@
         <v>233</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>234</v>
@@ -3306,7 +3309,7 @@
         <v>237</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>238</v>
@@ -3323,7 +3326,7 @@
         <v>240</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>241</v>
@@ -3340,7 +3343,7 @@
         <v>242</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>243</v>
@@ -3357,7 +3360,7 @@
         <v>245</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>246</v>
@@ -3374,7 +3377,7 @@
         <v>248</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>249</v>
@@ -3391,7 +3394,7 @@
         <v>251</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>252</v>
@@ -3408,7 +3411,7 @@
         <v>253</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>254</v>
@@ -3425,7 +3428,7 @@
         <v>255</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>256</v>
@@ -3442,7 +3445,7 @@
         <v>258</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>259</v>
@@ -3459,7 +3462,7 @@
         <v>261</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>262</v>
@@ -3476,7 +3479,7 @@
         <v>264</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>265</v>
@@ -3493,7 +3496,7 @@
         <v>267</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>268</v>
@@ -3510,7 +3513,7 @@
         <v>270</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>271</v>
@@ -3527,7 +3530,7 @@
         <v>273</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>274</v>
@@ -3544,7 +3547,7 @@
         <v>275</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>276</v>
@@ -3561,7 +3564,7 @@
         <v>277</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>278</v>
@@ -3578,7 +3581,7 @@
         <v>279</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>280</v>
@@ -3595,7 +3598,7 @@
         <v>282</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>283</v>
@@ -3612,7 +3615,7 @@
         <v>287</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>288</v>
@@ -3629,7 +3632,7 @@
         <v>290</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>291</v>
@@ -3646,7 +3649,7 @@
         <v>293</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>294</v>
@@ -3663,7 +3666,7 @@
         <v>296</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>297</v>
@@ -3680,7 +3683,7 @@
         <v>298</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>299</v>
@@ -3697,7 +3700,7 @@
         <v>301</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>302</v>
@@ -3714,7 +3717,7 @@
         <v>304</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>305</v>
@@ -3731,7 +3734,7 @@
         <v>307</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>308</v>
@@ -3748,7 +3751,7 @@
         <v>310</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>311</v>
@@ -3765,7 +3768,7 @@
         <v>312</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>313</v>
@@ -3782,7 +3785,7 @@
         <v>314</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>315</v>
@@ -3799,7 +3802,7 @@
         <v>316</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>317</v>
@@ -3816,7 +3819,7 @@
         <v>318</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>319</v>
@@ -3833,7 +3836,7 @@
         <v>321</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>322</v>
@@ -3850,7 +3853,7 @@
         <v>324</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>325</v>
@@ -3867,7 +3870,7 @@
         <v>327</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>328</v>
@@ -3884,7 +3887,7 @@
         <v>330</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>331</v>
@@ -3901,7 +3904,7 @@
         <v>333</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>334</v>
@@ -3918,7 +3921,7 @@
         <v>337</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>338</v>
@@ -3935,7 +3938,7 @@
         <v>340</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>341</v>
@@ -3952,7 +3955,7 @@
         <v>343</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>344</v>
@@ -3969,7 +3972,7 @@
         <v>345</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>346</v>
@@ -3986,7 +3989,7 @@
         <v>347</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>348</v>
@@ -4003,7 +4006,7 @@
         <v>349</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>350</v>
@@ -4020,7 +4023,7 @@
         <v>352</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>353</v>
@@ -4037,7 +4040,7 @@
         <v>355</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>356</v>
@@ -4054,7 +4057,7 @@
         <v>357</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>358</v>
@@ -4071,7 +4074,7 @@
         <v>360</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>361</v>
@@ -4088,7 +4091,7 @@
         <v>362</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>363</v>
@@ -4105,7 +4108,7 @@
         <v>365</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>366</v>
@@ -4122,7 +4125,7 @@
         <v>367</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>368</v>
@@ -4139,7 +4142,7 @@
         <v>370</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>371</v>
@@ -4156,7 +4159,7 @@
         <v>373</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>374</v>
@@ -4173,7 +4176,7 @@
         <v>377</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>378</v>
@@ -4190,7 +4193,7 @@
         <v>380</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>381</v>
@@ -4207,7 +4210,7 @@
         <v>382</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>383</v>
@@ -4224,7 +4227,7 @@
         <v>384</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>385</v>
@@ -4241,7 +4244,7 @@
         <v>386</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>387</v>
@@ -4258,7 +4261,7 @@
         <v>388</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>389</v>
@@ -4275,7 +4278,7 @@
         <v>391</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>392</v>
@@ -4292,7 +4295,7 @@
         <v>394</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>395</v>
@@ -4309,7 +4312,7 @@
         <v>396</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>397</v>
@@ -4326,7 +4329,7 @@
         <v>398</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>399</v>
@@ -4343,7 +4346,7 @@
         <v>400</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>401</v>
@@ -4360,7 +4363,7 @@
         <v>402</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>403</v>
@@ -4377,7 +4380,7 @@
         <v>405</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>406</v>
@@ -4394,7 +4397,7 @@
         <v>407</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>408</v>
@@ -4408,104 +4411,104 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>43</v>
+        <v>413</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>37</v>
+        <v>201</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>369</v>
+        <v>419</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>420</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>426</v>
+        <v>43</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4513,16 +4516,16 @@
         <v>427</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>428</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -4530,13 +4533,13 @@
         <v>429</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>430</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>431</v>
@@ -4547,7 +4550,7 @@
         <v>432</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>433</v>
@@ -4564,33 +4567,33 @@
         <v>434</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>435</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>185</v>
+        <v>436</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>438</v>
+        <v>300</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -4598,7 +4601,7 @@
         <v>439</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>440</v>
@@ -4615,13 +4618,13 @@
         <v>441</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>443</v>
@@ -4632,16 +4635,16 @@
         <v>444</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>445</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>300</v>
+        <v>161</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -4649,33 +4652,33 @@
         <v>446</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>43</v>
+        <v>448</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>450</v>
+        <v>354</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -4683,33 +4686,33 @@
         <v>451</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>452</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>161</v>
+        <v>453</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>455</v>
+        <v>250</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -4717,44 +4720,44 @@
         <v>456</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>457</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>354</v>
+        <v>458</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>33</v>
@@ -4765,53 +4768,53 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>465</v>
+        <v>393</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C161" s="1" t="s">
+      <c r="D161" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C162" s="1" t="s">
+      <c r="D162" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -4819,33 +4822,33 @@
         <v>471</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>472</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>474</v>
+        <v>43</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -4853,33 +4856,33 @@
         <v>475</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>476</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>477</v>
+        <v>185</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C166" s="1" t="s">
+      <c r="D166" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -4887,7 +4890,7 @@
         <v>480</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>481</v>
@@ -4904,7 +4907,7 @@
         <v>482</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>483</v>
@@ -4913,500 +4916,585 @@
         <v>37</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>185</v>
+        <v>484</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D169" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="5">
+        <v>336</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E169" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="D170" s="1" t="s">
+      <c r="E171" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="5">
+        <v>5</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E170" s="1" t="s">
+      <c r="E172" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="4" t="s">
-        <v>511</v>
+      <c r="A173" s="6">
+        <v>337</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>512</v>
+        <v>503</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>507</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="1" t="s">
-        <v>10</v>
+      <c r="E173" s="6">
+        <v>122103</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="5">
-        <v>336</v>
+      <c r="A174" s="6">
+        <v>338</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>43</v>
+        <v>503</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" s="6">
+        <v>140417</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="5">
-        <v>5</v>
+      <c r="A175" s="6">
+        <v>340</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>43</v>
+        <v>509</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E175" s="6">
+        <v>501510</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C176" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="C176" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>7</v>
+      <c r="D176" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="E176" s="6">
-        <v>122103</v>
+        <v>501401</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>13</v>
+        <v>512</v>
       </c>
       <c r="E177" s="6">
-        <v>140417</v>
+        <v>493221</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>33</v>
+        <v>178</v>
       </c>
       <c r="E178" s="6">
-        <v>501510</v>
+        <v>781122</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c r="E179" s="6">
-        <v>501401</v>
+        <v>711322</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>519</v>
+        <v>5</v>
       </c>
       <c r="E180" s="6">
-        <v>493221</v>
+        <v>226401</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="E181" s="6">
-        <v>781122</v>
+        <v>752054</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C182" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E182" s="6">
+        <v>804451</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="7">
+        <v>347</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E183" s="6">
+        <v>600067</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="7">
+        <v>348</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E184" s="6">
+        <v>387540</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="7">
+        <v>349</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C185" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="D182" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="E182" s="6">
-        <v>711322</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
-        <v>344</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C183" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="D183" s="6" t="s">
+      <c r="D185" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E183" s="6">
-        <v>226401</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
-        <v>342</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C184" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E184" s="6">
-        <v>752054</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
-        <v>343</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C185" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="D185" s="6" t="s">
-        <v>223</v>
-      </c>
       <c r="E185" s="6">
-        <v>804451</v>
+        <v>209859</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>498</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E186" s="6">
-        <v>600067</v>
+        <v>122506</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="7">
-        <v>348</v>
+        <v>1003</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>498</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="D187" s="6" t="s">
-        <v>22</v>
+        <v>523</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="E187" s="6">
-        <v>387540</v>
+        <v>421302</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E188" s="6">
-        <v>209859</v>
+        <v>500034</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c r="E189" s="6">
-        <v>122506</v>
+        <v>712223</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="7">
-        <v>1003</v>
+        <v>353</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>26</v>
+        <v>527</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="E190" s="6">
-        <v>421302</v>
+        <v>641402</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>501</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E191" s="6">
-        <v>500034</v>
+        <v>562107</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="7">
-        <v>352</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>510</v>
+        <v>355</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>530</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="E192" s="6">
-        <v>712223</v>
+        <v>131101</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E193" s="6">
-        <v>641402</v>
+        <v>562114</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D194" s="6" t="s">
         <v>37</v>
       </c>
       <c r="E194" s="6">
-        <v>562107</v>
+        <v>562123</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="7">
-        <v>355</v>
-      </c>
-      <c r="B195" s="8" t="s">
-        <v>537</v>
+        <v>358</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E195" s="6">
-        <v>131101</v>
+        <v>562106</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E196" s="6">
-        <v>562114</v>
+        <v>121004</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D197" s="6" t="s">
         <v>37</v>
       </c>
       <c r="E197" s="6">
-        <v>562123</v>
+        <v>562122</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="7">
+        <v>361</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E198" s="6">
+        <v>421101</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="7">
+        <v>362</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E199" s="6">
+        <v>122413</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="7">
+        <v>363</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E200" s="6">
+        <v>712306</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="7">
+        <v>364</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E201" s="6">
+        <v>131103</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="7">
+        <v>365</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E202" s="6">
+        <v>711316</v>
       </c>
     </row>
   </sheetData>
